--- a/reports/pdf_change_20260818.xlsx
+++ b/reports/pdf_change_20260818.xlsx
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-203685560</v>
+        <v>-1501978400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.04%→0.00%</t>
+          <t>3.66%→3.57%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>156→143</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1501978400</v>
+        <v>-203685560</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>3.66%→3.57%</t>
+          <t>0.04%→0.00%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>156→143</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260818.xlsx
+++ b/reports/pdf_change_20260818.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1501978400</v>
+        <v>-203685560</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>3.66%→3.57%</t>
+          <t>0.04%→0.00%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>156→143</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-203685560</v>
+        <v>-1501978400</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.04%→0.00%</t>
+          <t>3.66%→3.57%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>156→143</t>
         </is>
       </c>
     </row>
@@ -1005,318 +1005,632 @@
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="20" t="n"/>
-      <c r="H18" s="20" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="20" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
-      <c r="H20" s="20" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,797억   ·   현금 41억(1.5%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 4종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>1297338000</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>0.09%→0.57%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>20→120</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>한국피아이엠</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-47</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-2436310800</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>1.31%→0.63%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>80→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>1381590000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>1.27%→1.77%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>250→350</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-1332752400</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>5.40%→4.90%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>375→341</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>메쥬</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>491567580</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>0.08%→0.26%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>24→77</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-255869040</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>0.44%→0.32%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>150→116</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>1349745600</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>0.82%→1.37%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>30→47</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>미래에셋벤처투자</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-362355000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>1.14%→1.01%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>250→221</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-634746000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>5.13%→4.88%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>110→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-928200000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>1.35%→1.02%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>20→15</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,353억   ·   현금 24억(1.0%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 7억(2.4%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n">
+      <c r="B34" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="C25" s="11" t="n">
+      <c r="C34" s="11" t="n">
         <v>42123000</v>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>7.62%→7.76%</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>780→795</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>새로닉스</t>
         </is>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H34" s="15" t="n">
         <v>-43</v>
       </c>
-      <c r="I25" s="15" t="n">
+      <c r="I34" s="15" t="n">
         <v>-34967600</v>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>2.69%→2.56%</t>
         </is>
       </c>
-      <c r="K25" s="13" t="inlineStr">
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>950→907</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="B26" s="11" t="n">
+      <c r="B35" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C26" s="11" t="n">
+      <c r="C35" s="11" t="n">
         <v>58292000</v>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>2.92%→3.12%</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>144→154</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>스피어</t>
         </is>
       </c>
-      <c r="H26" s="15" t="n">
+      <c r="H35" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I26" s="15" t="n">
+      <c r="I35" s="15" t="n">
         <v>-15777600</v>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>2.49%→2.43%</t>
         </is>
       </c>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>363→355</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>브이엠</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B36" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C27" s="11" t="n">
+      <c r="C36" s="11" t="n">
         <v>46854000</v>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>3.31%→3.47%</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>183→192</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H36" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I27" s="15" t="n">
+      <c r="I36" s="15" t="n">
         <v>-69008000</v>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>2.34%→2.10%</t>
         </is>
       </c>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>39→35</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 602억   ·   현금 10억(1.7%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n"/>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="20" t="n"/>
-      <c r="G32" s="20" t="n"/>
-      <c r="H32" s="20" t="n"/>
-      <c r="I32" s="20" t="n"/>
-      <c r="J32" s="20" t="n"/>
-      <c r="K32" s="20" t="n"/>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A22:K22"/>
+  <mergeCells count="18">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A39:K39"/>
     <mergeCell ref="A15:K15"/>
     <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A41:K41"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260818.xlsx
+++ b/reports/pdf_change_20260818.xlsx
@@ -1096,23 +1096,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1297338000</v>
+        <v>1381590000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.57%</t>
+          <t>1.27%→1.77%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>20→120</t>
+          <t>250→350</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1140,23 +1140,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1381590000</v>
+        <v>1297338000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.77%</t>
+          <t>0.09%→0.57%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>250→350</t>
+          <t>20→120</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1277,23 +1277,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-634746000</v>
+        <v>-928200000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>5.13%→4.88%</t>
+          <t>1.35%→1.02%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>110→105</t>
+          <t>20→15</t>
         </is>
       </c>
     </row>
@@ -1305,23 +1305,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-928200000</v>
+        <v>-634746000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>1.35%→1.02%</t>
+          <t>5.13%→4.88%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>110→105</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260818.xlsx
+++ b/reports/pdf_change_20260818.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,802억   ·   현금 136억(2.8%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 8종목  /  매도 6종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,778억   ·   현금 136억(2.8%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 8종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>42</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>441616560</v>
+        <v>443316720</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-27</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2359257300</v>
+        <v>-2368340100</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>39</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>954269550</v>
+        <v>957943350</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-18</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-452588400</v>
+        <v>-454330800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>478771200</v>
+        <v>480614400</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-203685560</v>
+        <v>-204469720</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>475446400</v>
+        <v>477276800</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1501978400</v>
+        <v>-1507760800</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>465679800</v>
+        <v>467472600</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-8</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-946736800</v>
+        <v>-950381600</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>472225500</v>
+        <v>474043500</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-3</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1240566000</v>
+        <v>-1245342000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>7</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2283722000</v>
+        <v>2292514000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>423392500</v>
+        <v>425022500</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,051억   ·   현금 10억(0.2%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,023억   ·   현금 10억(0.2%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -1007,7 +1007,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,797억   ·   현금 41억(1.5%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 4종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,774억   ·   현금 41억(1.5%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1103,7 +1103,7 @@
         <v>100</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1381590000</v>
+        <v>1391265000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>-47</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-2436310800</v>
+        <v>-2453371800</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>100</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1297338000</v>
+        <v>1306423000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1161,23 +1161,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1332752400</v>
+        <v>-257660840</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.90%</t>
+          <t>0.44%→0.32%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
         <v>53</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>491567580</v>
+        <v>495009930</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1205,23 +1205,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-255869040</v>
+        <v>-1342085400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.32%</t>
+          <t>5.40%→4.90%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1349745600</v>
+        <v>1359197600</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>-29</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-362355000</v>
+        <v>-364892500</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1277,23 +1277,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-928200000</v>
+        <v>-639191000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.35%→1.02%</t>
+          <t>5.13%→4.88%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>110→105</t>
         </is>
       </c>
     </row>
@@ -1305,30 +1305,30 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-634746000</v>
+        <v>-934700000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>5.13%→4.88%</t>
+          <t>1.35%→1.02%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>110→105</t>
+          <t>20→15</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,353억   ·   현금 24억(1.0%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,346억   ·   현금 24억(1.0%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>7.62%→7.76%</t>
+          <t>7.60%→7.75%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1469,11 +1469,11 @@
         <v>-43</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-34967600</v>
+        <v>-36732320</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.56%</t>
+          <t>2.82%→2.69%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1492,11 +1492,11 @@
         <v>10</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>58292000</v>
+        <v>55404000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>2.92%→3.12%</t>
+          <t>2.77%→2.96%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1513,11 +1513,11 @@
         <v>-8</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-15777600</v>
+        <v>-16081600</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>2.49%→2.43%</t>
+          <t>2.53%→2.48%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -1536,11 +1536,11 @@
         <v>9</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>46854000</v>
+        <v>46648800</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>3.31%→3.47%</t>
+          <t>3.29%→3.45%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1557,11 +1557,11 @@
         <v>-4</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-69008000</v>
+        <v>-74176000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>2.34%→2.10%</t>
+          <t>2.51%→2.25%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 602억   ·   현금 10억(1.7%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 10억(1.7%)      당일 2026-08-18  vs  전영업일 2026-08-14      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>

--- a/reports/pdf_change_20260818.xlsx
+++ b/reports/pdf_change_20260818.xlsx
@@ -1161,23 +1161,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-257660840</v>
+        <v>-1342085400</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.32%</t>
+          <t>5.40%→4.90%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
@@ -1205,23 +1205,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1342085400</v>
+        <v>-257660840</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.90%</t>
+          <t>0.44%→0.32%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260818.xlsx
+++ b/reports/pdf_change_20260818.xlsx
@@ -772,23 +772,23 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-204469720</v>
+        <v>-1507760800</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.04%→0.00%</t>
+          <t>3.66%→3.57%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>156→143</t>
         </is>
       </c>
     </row>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1507760800</v>
+        <v>-204469720</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>3.66%→3.57%</t>
+          <t>0.04%→0.00%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>156→143</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1161,23 +1161,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>PS일렉트로닉스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1342085400</v>
+        <v>-257660840</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>5.40%→4.90%</t>
+          <t>0.44%→0.32%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>375→341</t>
+          <t>150→116</t>
         </is>
       </c>
     </row>
@@ -1205,23 +1205,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>PS일렉트로닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-257660840</v>
+        <v>-1342085400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.32%</t>
+          <t>5.40%→4.90%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>150→116</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20260818.xlsx
+++ b/reports/pdf_change_20260818.xlsx
@@ -1096,23 +1096,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>미코</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1391265000</v>
+        <v>1306423000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.77%</t>
+          <t>0.09%→0.57%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>250→350</t>
+          <t>20→120</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1140,23 +1140,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>100</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1306423000</v>
+        <v>1391265000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.57%</t>
+          <t>1.27%→1.77%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>20→120</t>
+          <t>250→350</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1277,23 +1277,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-639191000</v>
+        <v>-934700000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>5.13%→4.88%</t>
+          <t>1.35%→1.02%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>110→105</t>
+          <t>20→15</t>
         </is>
       </c>
     </row>
@@ -1305,23 +1305,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-934700000</v>
+        <v>-639191000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>1.35%→1.02%</t>
+          <t>5.13%→4.88%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>110→105</t>
         </is>
       </c>
     </row>
